--- a/Result/profitability/2211.xlsx
+++ b/Result/profitability/2211.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3874,24 +3874,24 @@
         <v>3629</v>
       </c>
       <c r="D28" t="n">
-        <v>2502</v>
+        <v>2481</v>
       </c>
       <c r="E28" t="n">
-        <v>1127</v>
+        <v>1148</v>
       </c>
       <c r="F28" t="n">
-        <v>31.06</v>
+        <v>31.64</v>
       </c>
       <c r="G28" t="n">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>26.92%</t>
+          <t>27.50%</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="J28" t="n">
         <v>1612</v>
@@ -3906,7 +3906,7 @@
         <v>1.72125</v>
       </c>
       <c r="N28" t="n">
-        <v>30.14875</v>
+        <v>30.22125</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -3939,10 +3939,10 @@
         <v>1.006711409395973</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.48</v>
+        <v>6.060000000000002</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.2142298670836591</v>
+        <v>0.2369038311180611</v>
       </c>
       <c r="AA28" t="n">
         <v>1.08</v>
@@ -3951,10 +3951,10 @@
         <v>0.5654450261780106</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.259999999999998</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.008441558441558472</v>
+        <v>0.02727272727272734</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4001,24 +4001,24 @@
         <v>3998</v>
       </c>
       <c r="D29" t="n">
-        <v>2842</v>
+        <v>2863</v>
       </c>
       <c r="E29" t="n">
-        <v>1156</v>
+        <v>1135</v>
       </c>
       <c r="F29" t="n">
-        <v>28.92</v>
+        <v>28.4</v>
       </c>
       <c r="G29" t="n">
-        <v>1006</v>
+        <v>985</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25.17%</t>
+          <t>24.64%</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="J29" t="n">
         <v>1520</v>
@@ -4033,7 +4033,7 @@
         <v>1.805</v>
       </c>
       <c r="N29" t="n">
-        <v>29.21</v>
+        <v>29.2175</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -4066,10 +4066,10 @@
         <v>-0.04013377926421413</v>
       </c>
       <c r="Y29" t="n">
-        <v>-2.139999999999997</v>
+        <v>-3.240000000000002</v>
       </c>
       <c r="Z29" t="n">
-        <v>-0.06889890534449439</v>
+        <v>-0.1024020227560051</v>
       </c>
       <c r="AA29" t="n">
         <v>0.9200000000000002</v>
@@ -4078,10 +4078,10 @@
         <v>0.4717948717948719</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.57</v>
+        <v>5.049999999999997</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.2385438972162741</v>
+        <v>0.21627408993576</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4160,7 +4160,7 @@
         <v>1.84</v>
       </c>
       <c r="N30" t="n">
-        <v>27.3275</v>
+        <v>27.335</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4193,10 +4193,10 @@
         <v>-0.5679442508710801</v>
       </c>
       <c r="Y30" t="n">
-        <v>-3.670000000000002</v>
+        <v>-3.149999999999999</v>
       </c>
       <c r="Z30" t="n">
-        <v>-0.1269017980636239</v>
+        <v>-0.1109154929577464</v>
       </c>
       <c r="AA30" t="n">
         <v>0.1299999999999999</v>
@@ -4287,7 +4287,7 @@
         <v>1.82875</v>
       </c>
       <c r="N31" t="n">
-        <v>26.62625</v>
+        <v>26.63375</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4365,6 +4365,133 @@
       </c>
       <c r="AM31" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4336</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3135</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1201</v>
+      </c>
+      <c r="F32" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="G32" t="n">
+        <v>914</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>21.07%</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>353</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1267</v>
+      </c>
+      <c r="K32" t="n">
+        <v>912</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.86375</v>
+      </c>
+      <c r="N32" t="n">
+        <v>26.2475</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.046728971962616</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4.560000000000002</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.196976241900648</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-0.8000000000000003</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>-0.2675585284280937</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>-0.1242098609355247</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
